--- a/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -549,14 +549,14 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|仲|―</t>
+          <t xml:space="preserve">姑|仲|–</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I2" s="2"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―仲|姑仲△</t>
+          <t xml:space="preserve">–仲|姑仲△</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―仲
+          <t xml:space="preserve">–仲
 姑仲△</t>
         </is>
       </c>
@@ -766,13 +766,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢|―無</t>
+          <t xml:space="preserve">無潢|–無</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I8" s="2"/>
@@ -837,12 +837,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="2"/>
@@ -947,12 +947,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―湳|㳞</t>
+          <t xml:space="preserve">–湳|㳞</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―湳
+          <t xml:space="preserve">–湳
 㳞</t>
         </is>
       </c>
@@ -983,14 +983,14 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌㳞|㴌潢|―</t>
+          <t xml:space="preserve">㴌㳞|㴌潢|–</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌㳞
 㴌潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="3"/>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|姑</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無潢無</t>
+          <t xml:space="preserve">–|無潢無</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無潢無</t>
         </is>
       </c>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢無南</t>
+          <t xml:space="preserve">–|潢無南</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢無南</t>
         </is>
       </c>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I23" s="2"/>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰潢</t>
+          <t xml:space="preserve">–|汰潢</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰潢</t>
         </is>
       </c>
@@ -1562,13 +1562,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―湳|㳞</t>
+          <t xml:space="preserve">–|–湳|㳞</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―湳
+          <t xml:space="preserve">–
+–湳
 㳞</t>
         </is>
       </c>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I32" s="2"/>
@@ -1775,13 +1775,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢|―</t>
+          <t xml:space="preserve">無潢|–</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I36" s="2"/>
@@ -1811,13 +1811,13 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無南|―</t>
+          <t xml:space="preserve">無南|–</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I37" s="2"/>
@@ -1917,12 +1917,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無|潢無</t>
+          <t xml:space="preserve">–無|潢無</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無
+          <t xml:space="preserve">–無
 潢無</t>
         </is>
       </c>
@@ -1993,13 +1993,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢|―無</t>
+          <t xml:space="preserve">無潢|–無</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I42" s="2"/>
@@ -2064,13 +2064,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳㳞|―㴌</t>
+          <t xml:space="preserve">湳㳞|–㴌</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">湳㳞
-―㴌</t>
+–㴌</t>
         </is>
       </c>
       <c r="I44" s="2"/>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㴌</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -2278,12 +2278,12 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I50" s="2"/>
@@ -2349,13 +2349,13 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢|―無</t>
+          <t xml:space="preserve">無潢|–無</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I52" s="2"/>
@@ -2420,13 +2420,13 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢|―無南</t>
+          <t xml:space="preserve">–潢|–無南</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢
-―無南</t>
+          <t xml:space="preserve">–潢
+–無南</t>
         </is>
       </c>
       <c r="I54" s="2"/>
@@ -2564,13 +2564,13 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢|―</t>
+          <t xml:space="preserve">無潢|–</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I58" s="2"/>
@@ -2600,13 +2600,13 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌潢|―</t>
+          <t xml:space="preserve">㴌潢|–</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I59" s="3"/>
@@ -2640,13 +2640,13 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―無|潢無</t>
+          <t xml:space="preserve">–|–無|潢無</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―無
+          <t xml:space="preserve">–
+–無
 潢無</t>
         </is>
       </c>
@@ -2855,12 +2855,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢無|南潢</t>
+          <t xml:space="preserve">–|潢無|南潢</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢無
 南潢</t>
         </is>
@@ -2927,13 +2927,13 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―潢|無南</t>
+          <t xml:space="preserve">–|–潢|無南</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―潢
+          <t xml:space="preserve">–
+–潢
 無南</t>
         </is>
       </c>
@@ -3142,12 +3142,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I74" s="2"/>
@@ -3177,12 +3177,12 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑|仲姑△</t>
+          <t xml:space="preserve">–姑|仲姑△</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑
+          <t xml:space="preserve">–姑
 仲姑△</t>
         </is>
       </c>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢無|南無</t>
+          <t xml:space="preserve">–潢無|南無</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢無
+          <t xml:space="preserve">–潢無
 南無</t>
         </is>
       </c>
@@ -3356,13 +3356,13 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―潢|無南</t>
+          <t xml:space="preserve">–|–潢|無南</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―潢
+          <t xml:space="preserve">–
+–潢
 無南</t>
         </is>
       </c>
@@ -3509,13 +3509,13 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―姑|仲</t>
+          <t xml:space="preserve">–|–姑|仲</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―姑
+          <t xml:space="preserve">–
+–姑
 仲</t>
         </is>
       </c>
@@ -3697,12 +3697,12 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I89" s="2"/>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I92" s="2"/>
@@ -3936,7 +3936,7 @@
       <c r="F3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="G3" s="8"/>
@@ -3949,7 +3949,7 @@
       <c r="J3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="K3" s="8"/>
@@ -3963,7 +3963,7 @@
         <is>
           <t xml:space="preserve">㴌㳞
 㴌潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="O3" s="11"/>
@@ -3971,7 +3971,7 @@
         <is>
           <t xml:space="preserve">姑
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="Q3" s="8"/>
@@ -3993,7 +3993,7 @@
       <c r="F4" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="G4" s="12"/>
@@ -4002,13 +4002,13 @@
       <c r="J4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
-―</t>
+–</t>
         </is>
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰潢</t>
         </is>
       </c>
@@ -4026,8 +4026,8 @@
       <c r="A5" s="0"/>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―姑
+          <t xml:space="preserve">–
+–姑
 仲</t>
         </is>
       </c>
@@ -4045,8 +4045,8 @@
       <c r="E5" s="10"/>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―無
+          <t xml:space="preserve">–
+–無
 潢無</t>
         </is>
       </c>
@@ -4073,7 +4073,7 @@
       <c r="M5" s="10"/>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -4150,7 +4150,7 @@
       <c r="C7" s="9"/>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E7" s="9"/>
@@ -4162,13 +4162,13 @@
       <c r="G7" s="9"/>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無
+          <t xml:space="preserve">–無
 潢無</t>
         </is>
       </c>
@@ -4181,7 +4181,7 @@
       <c r="M7" s="12"/>
       <c r="N7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無潢無</t>
         </is>
       </c>
@@ -4205,7 +4205,7 @@
       <c r="C8" s="10"/>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑
+          <t xml:space="preserve">–姑
 仲姑△</t>
         </is>
       </c>
@@ -4233,8 +4233,8 @@
       <c r="K8" s="13"/>
       <c r="L8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―湳
+          <t xml:space="preserve">–
+–湳
 㳞</t>
         </is>
       </c>
@@ -4248,7 +4248,7 @@
       <c r="O8" s="10"/>
       <c r="P8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―仲
+          <t xml:space="preserve">–仲
 姑仲△</t>
         </is>
       </c>
@@ -4284,14 +4284,14 @@
       <c r="H9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="K9" s="8"/>
@@ -4310,7 +4310,7 @@
       <c r="P9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="Q9" s="8"/>
@@ -4319,7 +4319,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C10" s="9"/>
@@ -4350,13 +4350,13 @@
       <c r="K10" s="9"/>
       <c r="L10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢無南</t>
         </is>
       </c>
@@ -4383,14 +4383,14 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢無
+          <t xml:space="preserve">–潢無
 南無</t>
         </is>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢無
 南潢</t>
         </is>
@@ -4398,8 +4398,8 @@
       <c r="G11" s="10"/>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢
-―無南</t>
+          <t xml:space="preserve">–潢
+–無南</t>
         </is>
       </c>
       <c r="I11" s="10"/>
@@ -4421,7 +4421,7 @@
       <c r="O11" s="10"/>
       <c r="P11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q11" s="10"/>
@@ -4457,7 +4457,7 @@
       <c r="J12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">湳㳞
-―㴌</t>
+–㴌</t>
         </is>
       </c>
       <c r="K12" s="8"/>
@@ -4485,22 +4485,22 @@
       <c r="A13" s="0"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―潢
+          <t xml:space="preserve">–
+–潢
 無南</t>
         </is>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―潢
+          <t xml:space="preserve">–
+–潢
 無南</t>
         </is>
       </c>
@@ -4526,7 +4526,7 @@
       <c r="M13" s="9"/>
       <c r="N13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O13" s="9"/>
@@ -4571,7 +4571,7 @@
       <c r="I14" s="10"/>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -4580,14 +4580,14 @@
       <c r="M14" s="10"/>
       <c r="N14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="O14" s="10"/>
       <c r="P14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―湳
+          <t xml:space="preserve">–湳
 㳞</t>
         </is>
       </c>

--- a/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3893,705 +3934,705 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">긴 아리랑</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아리</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="E3" s="22"/>
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 –</t>
         </is>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="G3" s="22"/>
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="I3" s="22"/>
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 –</t>
         </is>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="K3" s="22"/>
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="18" t="inlineStr">
+      <c r="M3" s="22"/>
+      <c r="N3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌㳞
 㴌潢
 –</t>
         </is>
       </c>
-      <c r="O3" s="11"/>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="O3" s="24"/>
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲
 –</t>
         </is>
       </c>
-      <c r="Q3" s="8"/>
+      <c r="Q3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="E4" s="26"/>
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢
 –</t>
         </is>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="G4" s="25"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 –</t>
         </is>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="K4" s="26"/>
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰潢</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="M4" s="26"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q4" s="9"/>
+      <c r="Q4" s="26"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –姑
 仲</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="27"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –無
 潢無</t>
         </is>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="27"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 無潢無</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="I5" s="27"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="27"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 △</t>
         </is>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="27"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="18" t="inlineStr">
+      <c r="O5" s="27"/>
+      <c r="P5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="Q5" s="13"/>
+      <c r="Q5" s="28"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲姑仲</t>
         </is>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="22"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
 無</t>
         </is>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="22"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢無
 南</t>
         </is>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="I6" s="22"/>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="K6" s="22"/>
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㳞</t>
         </is>
       </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="M6" s="22"/>
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="O6" s="22"/>
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q6" s="8"/>
+      <c r="Q6" s="22"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="26"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="26"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="26"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="26"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無
 潢無</t>
         </is>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="18" t="inlineStr">
+      <c r="K7" s="26"/>
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ﾉ</t>
         </is>
       </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="M7" s="25"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無潢無</t>
         </is>
       </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="O7" s="26"/>
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q7" s="9"/>
+      <c r="Q7" s="26"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑
 仲
 △</t>
         </is>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="27"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–姑
 仲姑△</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="27"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="27"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="I8" s="27"/>
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 △</t>
         </is>
       </c>
-      <c r="K8" s="13"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="28"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –湳
 㳞</t>
         </is>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="M8" s="27"/>
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
 無潢無</t>
         </is>
       </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="O8" s="27"/>
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–仲
 姑仲△</t>
         </is>
       </c>
-      <c r="Q8" s="10"/>
+      <c r="Q8" s="27"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아리</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲
 南無南</t>
         </is>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E9" s="22"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無南
 南潢</t>
         </is>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="G9" s="22"/>
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 –無</t>
         </is>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="I9" s="22"/>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 –無</t>
         </is>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="K9" s="22"/>
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M9" s="8"/>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="M9" s="22"/>
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O9" s="8"/>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="O9" s="22"/>
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 –無</t>
         </is>
       </c>
-      <c r="Q9" s="8"/>
+      <c r="Q9" s="22"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="26"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢無
 南</t>
         </is>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="26"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="26"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="26"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="K10" s="26"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M10" s="26"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢無南</t>
         </is>
       </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="O10" s="26"/>
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q10" s="9"/>
+      <c r="Q10" s="26"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲
 姑仲姑</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–潢無
 南無</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="27"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢無
 南潢</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="27"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–潢
 –無南</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="I11" s="27"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌㳞㴌
 潢無</t>
         </is>
       </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="M11" s="27"/>
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑
 仲</t>
         </is>
       </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="O11" s="27"/>
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q11" s="10"/>
+      <c r="Q11" s="27"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃僙南
 仲姑</t>
         </is>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="24"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="22"/>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑仲
 南仲</t>
         </is>
       </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="I12" s="22"/>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳㳞
 –㴌</t>
         </is>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M12" s="8"/>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="M12" s="22"/>
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="8"/>
-      <c r="P12" s="18" t="inlineStr">
+      <c r="O12" s="22"/>
+      <c r="P12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃無
 南潢‹</t>
         </is>
       </c>
-      <c r="Q12" s="11"/>
+      <c r="Q12" s="24"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="26"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –潢
 無南</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="26"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –潢
 無南</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="26"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 ·</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="26"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="26"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="26"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="O13" s="26"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
+      <c r="Q13" s="26"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑
 仲
 △</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑仲
 姑
 △</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="27"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑
 仲</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="27"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="27"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="K14" s="27"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="27"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–湳
 㳞</t>
         </is>
       </c>
-      <c r="Q14" s="10"/>
+      <c r="Q14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
@@ -3911,28 +3911,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
       <c r="C4" s="25"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="26"/>
@@ -4058,12 +4058,12 @@
       <c r="O4" s="26"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q4" s="26"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4101,7 +4101,7 @@
       <c r="I5" s="27"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K5" s="27"/>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="Q5" s="28"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K6" s="22"/>
@@ -4181,11 +4181,11 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C7" s="26"/>
@@ -4229,12 +4229,12 @@
       <c r="O7" s="26"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q7" s="26"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4253,14 +4253,14 @@
       <c r="E8" s="27"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="G8" s="27"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Q8" s="27"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="Q10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="Q11" s="27"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="Q12" s="24"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-·</t>
+–</t>
         </is>
       </c>
       <c r="I13" s="26"/>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="Q13" s="26"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
       <c r="G14" s="27"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
@@ -913,13 +913,13 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃無|南潢‹</t>
+          <t xml:space="preserve">黃無|南潢</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">黃無
-南潢‹</t>
+南潢</t>
         </is>
       </c>
       <c r="I11" s="3"/>
@@ -4517,7 +4517,7 @@
       <c r="P12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃無
-南潢‹</t>
+南潢</t>
         </is>
       </c>
       <c r="Q12" s="24"/>

--- a/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
@@ -3965,7 +3965,8 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">아리</t>
+          <t xml:space="preserve">아
+리</t>
         </is>
       </c>
       <c r="D3" s="21" t="inlineStr">
@@ -4305,7 +4306,8 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">아리</t>
+          <t xml:space="preserve">아
+리</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">

--- a/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
@@ -552,7 +552,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -562,7 +561,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -571,7 +569,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -591,7 +588,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -600,17 +597,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -643,6 +640,12 @@
       <sz val="24"/>
       <name val="궁서체"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -735,7 +738,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -793,6 +796,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3953,452 +4000,452 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
     </row>
     <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="19"/>
+      <c r="F3" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="7" t="s">
+      <c r="G3" s="19"/>
+      <c r="H3" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="7" t="s">
+      <c r="I3" s="19"/>
+      <c r="J3" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="7" t="s">
+      <c r="K3" s="19"/>
+      <c r="L3" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="9" t="s">
+      <c r="M3" s="19"/>
+      <c r="N3" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="O3" s="10"/>
-      <c r="P3" s="7" t="s">
+      <c r="O3" s="21"/>
+      <c r="P3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="8"/>
+      <c r="Q3" s="19"/>
     </row>
     <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="22"/>
+      <c r="D4" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="9" t="s">
+      <c r="E4" s="23"/>
+      <c r="F4" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="7" t="s">
+      <c r="G4" s="22"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="7" t="s">
+      <c r="K4" s="23"/>
+      <c r="L4" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="7" t="s">
+      <c r="M4" s="23"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="Q4" s="12"/>
+      <c r="Q4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="24"/>
+      <c r="F5" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="7" t="s">
+      <c r="G5" s="24"/>
+      <c r="H5" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="I5" s="13"/>
-      <c r="J5" s="7" t="s">
+      <c r="I5" s="24"/>
+      <c r="J5" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="7" t="s">
+      <c r="K5" s="24"/>
+      <c r="L5" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="7" t="s">
+      <c r="M5" s="24"/>
+      <c r="N5" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="O5" s="13"/>
-      <c r="P5" s="9" t="s">
+      <c r="O5" s="24"/>
+      <c r="P5" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="Q5" s="14"/>
+      <c r="Q5" s="25"/>
     </row>
     <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="19"/>
+      <c r="D6" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="7" t="s">
+      <c r="G6" s="19"/>
+      <c r="H6" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="7" t="s">
+      <c r="I6" s="19"/>
+      <c r="J6" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="7" t="s">
+      <c r="K6" s="19"/>
+      <c r="L6" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="7" t="s">
+      <c r="M6" s="19"/>
+      <c r="N6" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="7" t="s">
+      <c r="O6" s="19"/>
+      <c r="P6" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="Q6" s="8"/>
+      <c r="Q6" s="19"/>
     </row>
     <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="7" t="s">
+      <c r="C7" s="23"/>
+      <c r="D7" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="7" t="s">
+      <c r="E7" s="23"/>
+      <c r="F7" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="7" t="s">
+      <c r="G7" s="23"/>
+      <c r="H7" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="7" t="s">
+      <c r="I7" s="23"/>
+      <c r="J7" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="9" t="s">
+      <c r="K7" s="23"/>
+      <c r="L7" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="M7" s="11"/>
-      <c r="N7" s="7" t="s">
+      <c r="M7" s="22"/>
+      <c r="N7" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="O7" s="12"/>
-      <c r="P7" s="7" t="s">
+      <c r="O7" s="23"/>
+      <c r="P7" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="Q7" s="12"/>
+      <c r="Q7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="24"/>
+      <c r="D8" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="24"/>
+      <c r="F8" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="7" t="s">
+      <c r="G8" s="24"/>
+      <c r="H8" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="9" t="s">
+      <c r="I8" s="24"/>
+      <c r="J8" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="K8" s="14"/>
-      <c r="L8" s="7" t="s">
+      <c r="K8" s="25"/>
+      <c r="L8" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="7" t="s">
+      <c r="M8" s="24"/>
+      <c r="N8" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="O8" s="13"/>
-      <c r="P8" s="7" t="s">
+      <c r="O8" s="24"/>
+      <c r="P8" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="Q8" s="13"/>
+      <c r="Q8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="7" t="s">
+      <c r="E9" s="19"/>
+      <c r="F9" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="7" t="s">
+      <c r="G9" s="19"/>
+      <c r="H9" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="7" t="s">
+      <c r="I9" s="19"/>
+      <c r="J9" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="7" t="s">
+      <c r="K9" s="19"/>
+      <c r="L9" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="8"/>
-      <c r="N9" s="7" t="s">
+      <c r="M9" s="19"/>
+      <c r="N9" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="O9" s="8"/>
-      <c r="P9" s="7" t="s">
+      <c r="O9" s="19"/>
+      <c r="P9" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="Q9" s="8"/>
+      <c r="Q9" s="19"/>
     </row>
     <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="23"/>
+      <c r="D10" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="7" t="s">
+      <c r="E10" s="23"/>
+      <c r="F10" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="23"/>
+      <c r="H10" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="23"/>
+      <c r="J10" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="K10" s="12"/>
-      <c r="L10" s="7" t="s">
+      <c r="K10" s="23"/>
+      <c r="L10" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="7" t="s">
+      <c r="M10" s="23"/>
+      <c r="N10" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="O10" s="12"/>
-      <c r="P10" s="7" t="s">
+      <c r="O10" s="23"/>
+      <c r="P10" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="Q10" s="12"/>
+      <c r="Q10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="7" t="s">
+      <c r="E11" s="24"/>
+      <c r="F11" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="7" t="s">
+      <c r="G11" s="24"/>
+      <c r="H11" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="7" t="s">
+      <c r="I11" s="24"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="7" t="s">
+      <c r="M11" s="24"/>
+      <c r="N11" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="O11" s="13"/>
-      <c r="P11" s="7" t="s">
+      <c r="O11" s="24"/>
+      <c r="P11" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="Q11" s="13"/>
+      <c r="Q11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="7" t="s">
+      <c r="C12" s="21"/>
+      <c r="D12" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7" t="s">
+      <c r="E12" s="19"/>
+      <c r="F12" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="7" t="s">
+      <c r="G12" s="19"/>
+      <c r="H12" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="7" t="s">
+      <c r="I12" s="19"/>
+      <c r="J12" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="7" t="s">
+      <c r="K12" s="19"/>
+      <c r="L12" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="M12" s="8"/>
-      <c r="N12" s="7" t="s">
+      <c r="M12" s="19"/>
+      <c r="N12" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="O12" s="8"/>
-      <c r="P12" s="9" t="s">
+      <c r="O12" s="19"/>
+      <c r="P12" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="Q12" s="10"/>
+      <c r="Q12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="23"/>
+      <c r="D13" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="7" t="s">
+      <c r="E13" s="23"/>
+      <c r="F13" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="7" t="s">
+      <c r="G13" s="23"/>
+      <c r="H13" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="I13" s="12"/>
-      <c r="J13" s="7" t="s">
+      <c r="I13" s="23"/>
+      <c r="J13" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="K13" s="12"/>
-      <c r="L13" s="7" t="s">
+      <c r="K13" s="23"/>
+      <c r="L13" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="7" t="s">
+      <c r="M13" s="23"/>
+      <c r="N13" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="O13" s="12"/>
-      <c r="P13" s="7" t="s">
+      <c r="O13" s="23"/>
+      <c r="P13" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="Q13" s="12"/>
+      <c r="Q13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="24"/>
+      <c r="D14" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="7" t="s">
+      <c r="E14" s="24"/>
+      <c r="F14" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="24"/>
+      <c r="H14" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="24"/>
+      <c r="J14" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="7" t="s">
+      <c r="K14" s="24"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="O14" s="13"/>
-      <c r="P14" s="7" t="s">
+      <c r="O14" s="24"/>
+      <c r="P14" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="Q14" s="13"/>
+      <c r="Q14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
@@ -662,10 +662,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
@@ -550,31 +550,9 @@
 리</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-–</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潢
-無</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+    <t xml:space="preserve">–
+–潢
+無南</t>
   </si>
   <si>
     <t xml:space="preserve">姑
@@ -3991,7 +3969,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:Q14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -4015,8 +3993,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -4036,7 +4014,7 @@
       <c r="P2" s="17"/>
       <c r="Q2" s="17"/>
     </row>
-    <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
       <c r="B3" s="18" t="s">
         <v>143</v>
       </c>
@@ -4072,7 +4050,7 @@
       </c>
       <c r="Q3" s="19"/>
     </row>
-    <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
       <c r="B4" s="20" t="s">
         <v>49</v>
       </c>
@@ -4102,7 +4080,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
       <c r="B5" s="18" t="s">
         <v>146</v>
       </c>
@@ -4138,7 +4116,7 @@
       </c>
       <c r="Q5" s="25"/>
     </row>
-    <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
       <c r="B6" s="18" t="s">
         <v>51</v>
       </c>
@@ -4172,7 +4150,7 @@
       </c>
       <c r="Q6" s="19"/>
     </row>
-    <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
       <c r="B7" s="18" t="s">
         <v>57</v>
       </c>
@@ -4206,7 +4184,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
       <c r="B8" s="18" t="s">
         <v>149</v>
       </c>
@@ -4240,7 +4218,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
       <c r="B9" s="18" t="s">
         <v>143</v>
       </c>
@@ -4276,7 +4254,7 @@
       </c>
       <c r="Q9" s="19"/>
     </row>
-    <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
       <c r="B10" s="18" t="s">
         <v>57</v>
       </c>
@@ -4310,7 +4288,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
       <c r="B11" s="18" t="s">
         <v>151</v>
       </c>
@@ -4344,7 +4322,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
       <c r="B12" s="20" t="s">
         <v>153</v>
       </c>
@@ -4378,7 +4356,7 @@
       </c>
       <c r="Q12" s="21"/>
     </row>
-    <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
       <c r="B13" s="18" t="s">
         <v>57</v>
       </c>
@@ -4412,7 +4390,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
       <c r="B14" s="18" t="s">
         <v>149</v>
       </c>
@@ -4450,7 +4428,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="76" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (늦중모리).xlsx
@@ -3975,26 +3975,26 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="81.63" customHeight="true">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -4014,7 +4014,7 @@
       <c r="P2" s="17"/>
       <c r="Q2" s="17"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="121.67" customHeight="true">
       <c r="B3" s="18" t="s">
         <v>143</v>
       </c>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="Q3" s="19"/>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="121.67" customHeight="true">
       <c r="B4" s="20" t="s">
         <v>49</v>
       </c>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="121.67" customHeight="true">
       <c r="B5" s="18" t="s">
         <v>146</v>
       </c>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="Q5" s="25"/>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="121.67" customHeight="true">
       <c r="B6" s="18" t="s">
         <v>51</v>
       </c>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="Q6" s="19"/>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="121.67" customHeight="true">
       <c r="B7" s="18" t="s">
         <v>57</v>
       </c>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="121.67" customHeight="true">
       <c r="B8" s="18" t="s">
         <v>149</v>
       </c>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="121.67" customHeight="true">
       <c r="B9" s="18" t="s">
         <v>143</v>
       </c>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="Q9" s="19"/>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="121.67" customHeight="true">
       <c r="B10" s="18" t="s">
         <v>57</v>
       </c>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="121.67" customHeight="true">
       <c r="B11" s="18" t="s">
         <v>151</v>
       </c>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="121.67" customHeight="true">
       <c r="B12" s="20" t="s">
         <v>153</v>
       </c>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="Q12" s="21"/>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="121.67" customHeight="true">
       <c r="B13" s="18" t="s">
         <v>57</v>
       </c>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="121.67" customHeight="true">
       <c r="B14" s="18" t="s">
         <v>149</v>
       </c>
@@ -4428,7 +4428,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
